--- a/artfynd/A 36365-2024 artfynd.xlsx
+++ b/artfynd/A 36365-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124099882</v>
+        <v>124099883</v>
       </c>
       <c r="B2" t="n">
-        <v>58033</v>
+        <v>58323</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -773,6 +774,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124099883</v>
+        <v>124099882</v>
       </c>
       <c r="B3" t="n">
-        <v>58323</v>
+        <v>58033</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +821,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -898,11 +903,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36365-2024 artfynd.xlsx
+++ b/artfynd/A 36365-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124099883</v>
+        <v>124099882</v>
       </c>
       <c r="B2" t="n">
-        <v>58345</v>
+        <v>58055</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>208245</v>
+        <v>102990</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,7 +713,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -774,11 +773,6 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -805,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124099882</v>
+        <v>124099883</v>
       </c>
       <c r="B3" t="n">
-        <v>58055</v>
+        <v>58345</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -821,16 +815,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -843,6 +837,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -903,6 +898,11 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36365-2024 artfynd.xlsx
+++ b/artfynd/A 36365-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>124099882</v>
+        <v>124099883</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
+        <v>58345</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,16 +691,16 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102990</v>
+        <v>208245</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Järnsparv</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Prunella modularis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -713,6 +713,7 @@
           <t>1</t>
         </is>
       </c>
+      <c r="J2" t="inlineStr"/>
       <c r="K2" t="inlineStr"/>
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
@@ -773,6 +774,11 @@
       <c r="AB2" t="inlineStr">
         <is>
           <t>15:15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +805,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>124099883</v>
+        <v>124099882</v>
       </c>
       <c r="B3" t="n">
-        <v>58345</v>
+        <v>58055</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -815,16 +821,16 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>208245</v>
+        <v>102990</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Järnsparv</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Prunella modularis</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -837,7 +843,6 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J3" t="inlineStr"/>
       <c r="K3" t="inlineStr"/>
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
@@ -898,11 +903,6 @@
       <c r="AB3" t="inlineStr">
         <is>
           <t>15:15</t>
-        </is>
-      </c>
-      <c r="AC3" t="inlineStr">
-        <is>
-          <t>I nyanlagd våtmark (återvätningsavtal med Skogsstyrelsen)</t>
         </is>
       </c>
       <c r="AD3" t="b">

--- a/artfynd/A 36365-2024 artfynd.xlsx
+++ b/artfynd/A 36365-2024 artfynd.xlsx
@@ -678,16 +678,11 @@
         <v>124099882</v>
       </c>
       <c r="B2" t="n">
-        <v>58055</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58497</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -802,12 +797,7 @@
         <v>124099883</v>
       </c>
       <c r="B3" t="n">
-        <v>58345</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>58790</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 36365-2024 artfynd.xlsx
+++ b/artfynd/A 36365-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AZ3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -791,6 +796,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124099882</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -916,8 +926,17 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124099883</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>